--- a/TODO.xlsx
+++ b/TODO.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\TrueQuests\TrueQuests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34654955-636E-4B1B-AC6E-22DA3ECEDC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9299286E-CCAF-4AE2-ACC0-BB900EDC5359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Dialogues Examples" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
   <si>
     <t>Personal Quests for faction leaders</t>
   </si>
@@ -40,13 +41,127 @@
   </si>
   <si>
     <t>rewards for specific quest should not give that same item that was requested</t>
+  </si>
+  <si>
+    <t>TQ_VanillaContent.lua</t>
+  </si>
+  <si>
+    <t>        {</t>
+  </si>
+  <si>
+    <t>        },</t>
+  </si>
+  <si>
+    <t>    },</t>
+  </si>
+  <si>
+    <t>})</t>
+  </si>
+  <si>
+    <t>            },</t>
+  </si>
+  <si>
+    <t>TQ.registerDialogueTopic({</t>
+  </si>
+  <si>
+    <t>    id = "about",</t>
+  </si>
+  <si>
+    <t>    text = "Tell me about yourself.",</t>
+  </si>
+  <si>
+    <t>    lineKey = "about",</t>
+  </si>
+  <si>
+    <t>    priority = 10,</t>
+  </si>
+  <si>
+    <t>    children = {</t>
+  </si>
+  <si>
+    <t>            id = "medics_needs",</t>
+  </si>
+  <si>
+    <t>            factionId = "medics",</t>
+  </si>
+  <si>
+    <t>            text = "What does the clinic need most?",</t>
+  </si>
+  <si>
+    <t>            npc = "Clean cloth, disinfectant, painkillers. In that order. Everything else is comfort.",</t>
+  </si>
+  <si>
+    <t>            priority = 10,</t>
+  </si>
+  <si>
+    <t>            id = "medics_people",</t>
+  </si>
+  <si>
+    <t>            text = "How are your people holding up?",</t>
+  </si>
+  <si>
+    <t>            npc = "Tired. Too tired to waste supplies, not tired enough to stop answering calls.",</t>
+  </si>
+  <si>
+    <t>            priority = 20,</t>
+  </si>
+  <si>
+    <t>            id = "independent_trust",</t>
+  </si>
+  <si>
+    <t>            factionId = "independent",</t>
+  </si>
+  <si>
+    <t>            text = "You trust anyone out there?",</t>
+  </si>
+  <si>
+    <t>            npc = "Trust? No. But I keep a list of people who did not make things worse.",</t>
+  </si>
+  <si>
+    <t>    id = "medics_rumors",</t>
+  </si>
+  <si>
+    <t>    factionId = "medics",</t>
+  </si>
+  <si>
+    <t>    text = "Is there anything happening lately?",</t>
+  </si>
+  <si>
+    <t>    npc = {</t>
+  </si>
+  <si>
+    <t>        "Someone came in talking about smoke north of the highway. Could be survivors, could be trouble.",</t>
+  </si>
+  <si>
+    <t>        "We heard gunfire after midnight. Short bursts. Organized, or scared. Hard to tell.",</t>
+  </si>
+  <si>
+    <t>        "A runner said the clinic road was clear this morning. I would not trust that by dusk.",</t>
+  </si>
+  <si>
+    <t>    priority = 20,</t>
+  </si>
+  <si>
+    <t>            id = "medics_rumors_more",</t>
+  </si>
+  <si>
+    <t>            text = "Anything else?",</t>
+  </si>
+  <si>
+    <t>            npc = {</t>
+  </si>
+  <si>
+    <t>                "A scavenger mentioned fresh tire tracks near the old service road.",</t>
+  </si>
+  <si>
+    <t>                "Two patients swear they heard a helicopter. I would not build a plan around it.",</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,13 +169,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF121314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -75,8 +207,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,4 +526,270 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A10CEA4-05F4-441E-958E-4AEFCA0ACC37}">
+  <dimension ref="B3:E53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E13" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E15" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E20" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E26" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E27" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E30" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E31" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E33" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E34" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E35" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E36" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E37" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E38" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E39" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E40" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E41" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E42" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E43" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E44" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E45" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E46" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E47" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E48" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E49" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E50" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E51" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E52" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E53" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/TODO.xlsx
+++ b/TODO.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\TrueQuests\TrueQuests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9299286E-CCAF-4AE2-ACC0-BB900EDC5359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9FE785-49DE-4770-91CB-CD012E954317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2565" yWindow="2415" windowWidth="33525" windowHeight="14355" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Dialogues Examples" sheetId="2" r:id="rId2"/>
+    <sheet name="Load Order" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>Personal Quests for faction leaders</t>
   </si>
@@ -155,6 +156,18 @@
   </si>
   <si>
     <t>                "Two patients swear they heard a helicopter. I would not build a plan around it.",</t>
+  </si>
+  <si>
+    <t>True NPC Framework</t>
+  </si>
+  <si>
+    <t>True Quest Framkework</t>
+  </si>
+  <si>
+    <t>True Qest - Vanilla Pack</t>
+  </si>
+  <si>
+    <t>True Quest -NPC Bridge</t>
   </si>
 </sst>
 </file>
@@ -792,4 +805,34 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2307DE78-5AA9-46CD-A898-CD0AD98037F8}">
+  <dimension ref="B2:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/TODO.xlsx
+++ b/TODO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\TrueQuests\TrueQuests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9FE785-49DE-4770-91CB-CD012E954317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B4C85A-7AB2-44BD-9C5D-9CFB0A83F611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="2415" windowWidth="33525" windowHeight="14355" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2565" yWindow="2415" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
   <si>
     <t>Personal Quests for faction leaders</t>
   </si>
@@ -168,6 +168,27 @@
   </si>
   <si>
     <t>True Quest -NPC Bridge</t>
+  </si>
+  <si>
+    <t>fix generator quest</t>
+  </si>
+  <si>
+    <t>bring lightbulps</t>
+  </si>
+  <si>
+    <t>могут кинуть на ревардах на квесте</t>
+  </si>
+  <si>
+    <t>добавить функцию фулл хил для медиков с высокой репутацией</t>
+  </si>
+  <si>
+    <t>можно выйти в меню со всеми членами если нажать back</t>
+  </si>
+  <si>
+    <t>взлом банкоматов для бабок</t>
+  </si>
+  <si>
+    <t>очистка трупов в радиусе клиники</t>
   </si>
 </sst>
 </file>
@@ -508,32 +529,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:G9"/>
+  <dimension ref="C2:U17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="R2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:21" x14ac:dyDescent="0.25">
       <c r="G5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="Q13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
